--- a/cmc-prep/05-for-brandon/settlement_model.xlsx
+++ b/cmc-prep/05-for-brandon/settlement_model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="347">
   <si>
     <t xml:space="preserve">ATTORNEY WORK-PRODUCT SUPPORT — PREPARED FOR COUNSEL — NOT A FILING — NOT LEGAL ADVICE — DEMONSTRATIVE ARITHMETIC ONLY, NOT AN OPINION OF VALUE — DO NOT SEND TO ANY PARTY</t>
   </si>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">~3.61 years</t>
   </si>
   <si>
-    <t xml:space="preserve">Implied start date (from 7/2/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~ Nov 21-22, 2022 — i.e., roughly 60 days after DOD. State the basis before opposing counsel reconstructs it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternative: DOD-start interest to 7/2/2026</t>
+    <t xml:space="preserve">RESOLVED 8/18/2026: 4% on $4.7M, DOD start, computed only THROUGH 5/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ computes $677,830.14 vs stated $677,830.41 (27 cents apart). Figure FIRST APPEARS in 5/1/2026 internal draft labeled "through May 1, 2026" and was reused verbatim in the 5/4 drafts, the 5/18 $5.75M letters, and the 7/2/2026 letter. See drive-sweep/drafts-proposals-sweep.md, item C-7. The earlier "implied start ~Nov 2022" reading is superseded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a FRESH computation through 7/2/2026 would give (same formula)</t>
   </si>
   <si>
     <t xml:space="preserve">~ $709,395 — what a DOD start would give</t>
@@ -851,6 +851,12 @@
     <t xml:space="preserve">Difference (DOD start - stated)</t>
   </si>
   <si>
+    <t xml:space="preserve">Consequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Under our own stated formula the 7/2/2026 offer under-credits interest by ~$31.9K (stale by 62 days). Refresh the interest figure before any renewed offer; opposing counsel can use the staleness to argue the number is negotiated, not contract math.</t>
+  </si>
+  <si>
     <t xml:space="preserve">FRAZER CAPITAL RECONCILIATION 3/25/2015 - 9/22/2022 (rev. 2/13/2025 — DRAFT, FOR INTERNAL DISCUSSION ONLY)</t>
   </si>
   <si>
@@ -1056,6 +1062,12 @@
   </si>
   <si>
     <t xml:space="preserve">UNVERIFIED — Corp. Code s.16601/16603/16701 could not be retrieved in this environment; counsel must verify (workspace OI-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal drafts corpus: "Leal Trust/Partnership" Drive folder (23 files) + "Land Acquisition" (3 files), all read 8/18/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-file Drive IDs and extracts: cmc-prep/01-verified-facts/drive-sweep/drafts-proposals-sweep.md. NOTE: internal AI-generated drafts — figures therein are NOT positions of record; used here only to source the C-7 interest-staleness finding and offset-stack history.</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1083,7 @@
     <numFmt numFmtId="169" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1140,6 +1152,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1318,7 +1337,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3254,7 +3273,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
@@ -3521,8 +3540,8 @@
         <v>269</v>
       </c>
       <c r="B36" s="26" t="n">
-        <f aca="false">DATE(2026,7,2)-B35*365.25</f>
-        <v>44888.0980997207</v>
+        <f aca="false">B33*B34*(DATE(2026,5,1)-DATE(2022,9,23))/365</f>
+        <v>677830.136986301</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>270</v>
@@ -3547,6 +3566,14 @@
       <c r="B38" s="15" t="n">
         <f aca="false">B37-B32</f>
         <v>31545.2745564075</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -3580,32 +3607,32 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
       <c r="B6" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B7" s="27" t="n">
         <v>5041721</v>
@@ -3620,12 +3647,12 @@
         <v>385199</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>346052</v>
@@ -3643,7 +3670,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>283908</v>
@@ -3661,7 +3688,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>-190800</v>
@@ -3679,7 +3706,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>5480881</v>
@@ -3694,12 +3721,12 @@
         <v>406492</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>-214285</v>
@@ -3717,7 +3744,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>-297218</v>
@@ -3735,7 +3762,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B14" s="27" t="n">
         <v>4969378</v>
@@ -3753,7 +3780,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>60000</v>
@@ -3771,7 +3798,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B16" s="14" t="n">
         <v>1020069</v>
@@ -3789,7 +3816,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>-276229</v>
@@ -3807,7 +3834,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B18" s="27" t="n">
         <v>5773218</v>
@@ -3825,7 +3852,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>93630</v>
@@ -3843,7 +3870,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>576611</v>
@@ -3861,7 +3888,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>-434875</v>
@@ -3879,7 +3906,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B22" s="27" t="n">
         <v>6008584</v>
@@ -3897,7 +3924,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B23" s="14" t="n">
         <v>1321713</v>
@@ -3915,7 +3942,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B24" s="14" t="n">
         <v>-319211</v>
@@ -3933,7 +3960,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B25" s="27" t="n">
         <v>7011086</v>
@@ -3951,7 +3978,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B26" s="14" t="n">
         <v>0</v>
@@ -3969,7 +3996,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B27" s="14" t="n">
         <v>80000</v>
@@ -3987,7 +4014,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B28" s="14" t="n">
         <v>560854</v>
@@ -4005,7 +4032,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B29" s="14" t="n">
         <v>-262516</v>
@@ -4023,7 +4050,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" s="27" t="n">
         <v>7389424</v>
@@ -4041,7 +4068,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B31" s="14" t="n">
         <v>1013445</v>
@@ -4059,7 +4086,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B32" s="14" t="n">
         <v>-235124</v>
@@ -4077,7 +4104,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B33" s="27" t="n">
         <v>8167745</v>
@@ -4095,7 +4122,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B34" s="14" t="n">
         <v>1011324</v>
@@ -4113,7 +4140,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B35" s="14" t="n">
         <v>-284904</v>
@@ -4131,7 +4158,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B36" s="27" t="n">
         <v>8894165</v>
@@ -4146,12 +4173,12 @@
         <v>794572</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" s="21" t="n">
         <f aca="false">B36</f>
@@ -4172,7 +4199,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B39" s="21" t="n">
         <f aca="false">B36-B38</f>
@@ -4191,43 +4218,43 @@
         <v>127509.625</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B41" s="21" t="n">
         <f aca="false">2079+418023-90729</f>
         <v>329373</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B42" s="28" t="n">
         <f aca="false">C39+B41</f>
         <v>-262591.875</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B44" s="21" t="n">
         <f aca="false">-(C10+C13+C17+C21+C24+C29+C32+C35)</f>
         <v>1371182</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4246,7 +4273,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
@@ -4260,87 +4287,95 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/cmc-prep/05-for-brandon/settlement_model.xlsx
+++ b/cmc-prep/05-for-brandon/settlement_model.xlsx
@@ -794,7 +794,7 @@
     <t xml:space="preserve">vs the $329,373 already credited inside the offset — difference</t>
   </si>
   <si>
-    <t xml:space="preserve">These are almost certainly the SAME income stream computed twice ($1,945.98 apart). Reconcile with Frazer before stacking both in any settlement.</t>
+    <t xml:space="preserve">RESOLVED 8/18/2026 (trust-admin sweep): they ARE the same figure — Appraisal Summary 1.22.25.xlsx "Bypass Income" sheet shows $329,373 less $1,945 of 2022 Bypass draws = $327,427.02 EXACTLY. The offset credits it once and the offer pays it again. Also: the Bypass Trust's own 1041s (2015-2019, Hazel as trustee) report NEGATIVE income, $0 DNI, "NO REPORTABLE INCOME" K-1s. Frazer must resolve whether credit and payment run through different accounts before any number is reused. See adverse analysis A-55 / OI-60; trust-admin-sweep.md sec.3.4.</t>
   </si>
   <si>
     <t xml:space="preserve">D. POST-DEATH PROFIT SHARE PER OUR OWN REVIEWED FS</t>
